--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484303_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484303_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. MARKOVETSKYY</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.8828</v>
+        <v>9.0314</v>
       </c>
       <c r="E2" t="n">
-        <v>8.4274</v>
+        <v>5.2323</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4554</v>
+        <v>3.7991</v>
       </c>
       <c r="G2" t="n">
-        <v>5.0542</v>
+        <v>7.4249</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8138</v>
+        <v>0.8425</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2404</v>
+        <v>6.5825</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8182</v>
+        <v>6.8458</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4423</v>
+        <v>0.5321</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3758</v>
+        <v>6.3136</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7639</v>
+        <v>0.5792</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6284999999999999</v>
+        <v>0.3103</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1354</v>
+        <v>0.2688</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.3674</v>
+        <v>0.3907</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5627</v>
+        <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2043</v>
+        <v>0.2743</v>
       </c>
       <c r="T2" t="n">
-        <v>1.329</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8753</v>
+        <v>0.2116</v>
       </c>
       <c r="V2" t="n">
-        <v>2.9917</v>
+        <v>0.9414</v>
       </c>
       <c r="W2" t="n">
-        <v>4.2104</v>
+        <v>0.2772</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>V. MARKOVETSKYY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.4482</v>
+        <v>7.9881</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3222</v>
+        <v>8.0229</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1259</v>
+        <v>-0.0348</v>
       </c>
       <c r="G3" t="n">
-        <v>7.4249</v>
+        <v>5.0542</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8425</v>
+        <v>3.8138</v>
       </c>
       <c r="I3" t="n">
-        <v>6.5825</v>
+        <v>1.2404</v>
       </c>
       <c r="J3" t="n">
-        <v>6.8458</v>
+        <v>5.8182</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5321</v>
+        <v>4.4423</v>
       </c>
       <c r="L3" t="n">
-        <v>6.3136</v>
+        <v>1.3758</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5792</v>
+        <v>-0.7639</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3103</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2688</v>
+        <v>-0.1354</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3907</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3441</v>
+        <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3089</v>
+        <v>1.3096</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8473000000000001</v>
+        <v>0.9245</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5384</v>
+        <v>0.385</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9414</v>
+        <v>2.9917</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2772</v>
+        <v>4.2104</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6642</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.6347</v>
+        <v>6.5918</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2145</v>
+        <v>6.4167</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4202</v>
+        <v>0.1751</v>
       </c>
       <c r="G4" t="n">
         <v>6.0667</v>
@@ -766,13 +766,13 @@
         <v>2.1488</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1112</v>
+        <v>-0.1541</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2312</v>
+        <v>0.4335</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3425</v>
+        <v>-0.5876</v>
       </c>
       <c r="V4" t="n">
         <v>2.4373</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.328</v>
+        <v>5.8913</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0398</v>
+        <v>3.5104</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2882</v>
+        <v>2.3809</v>
       </c>
       <c r="G5" t="n">
-        <v>3.709</v>
+        <v>4.6803</v>
       </c>
       <c r="H5" t="n">
-        <v>0.769</v>
+        <v>0.1082</v>
       </c>
       <c r="I5" t="n">
-        <v>2.94</v>
+        <v>4.572</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9901</v>
+        <v>4.5057</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1842</v>
+        <v>-0.2021</v>
       </c>
       <c r="L5" t="n">
-        <v>2.806</v>
+        <v>4.7078</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7189</v>
+        <v>0.1745</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5848</v>
+        <v>0.3103</v>
       </c>
       <c r="O5" t="n">
-        <v>0.134</v>
+        <v>-0.1358</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5395</v>
+        <v>3.1255</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3335</v>
+        <v>-1.1797</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0264</v>
+        <v>-0.2606</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6929</v>
+        <v>-0.9191</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="W5" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.2772</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.6388</v>
+        <v>5.4216</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8026</v>
+        <v>2.5342</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8362</v>
+        <v>2.8874</v>
       </c>
       <c r="G6" t="n">
-        <v>4.6803</v>
+        <v>3.709</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1082</v>
+        <v>0.769</v>
       </c>
       <c r="I6" t="n">
-        <v>4.572</v>
+        <v>2.94</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5057</v>
+        <v>2.9901</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2021</v>
+        <v>0.1842</v>
       </c>
       <c r="L6" t="n">
-        <v>4.7078</v>
+        <v>2.806</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1745</v>
+        <v>0.7189</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3103</v>
+        <v>0.5848</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1358</v>
+        <v>0.134</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1255</v>
+        <v>2.5395</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.4322</v>
+        <v>0.4271</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9684</v>
+        <v>0.5208</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.4638</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.8316</v>
+        <v>4.0883</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3117</v>
+        <v>1.5139</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5199</v>
+        <v>2.5744</v>
       </c>
       <c r="G7" t="n">
         <v>2.6507</v>
@@ -1000,13 +1000,13 @@
         <v>1.9534</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7726</v>
+        <v>-0.5159</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2008</v>
+        <v>0.0015</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5718</v>
+        <v>-0.5174</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.79</v>
+        <v>1.4714</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1295</v>
+        <v>-0.7805</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6604</v>
+        <v>2.2519</v>
       </c>
       <c r="G8" t="n">
         <v>2.3888</v>
@@ -1078,13 +1078,13 @@
         <v>2.5395</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7332</v>
+        <v>0.4147</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5794</v>
+        <v>0.6694</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1538</v>
+        <v>-0.2547</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9414</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1049</v>
+        <v>-0.2993</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7158</v>
+        <v>0.4125</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8207</v>
+        <v>-0.7118</v>
       </c>
       <c r="G9" t="n">
         <v>0.4413</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6724</v>
+        <v>0.478</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6741</v>
+        <v>0.3708</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0017</v>
+        <v>0.1073</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2186</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9155</v>
+        <v>-2.651</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5597</v>
+        <v>-2.4586</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3558</v>
+        <v>-0.1924</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7235</v>
@@ -1234,13 +1234,13 @@
         <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3603</v>
+        <v>-1.0958</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4842</v>
+        <v>-0.3831</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8761</v>
+        <v>-0.7127</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2224</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>37.5337</v>
+        <v>37.53360000000001</v>
       </c>
       <c r="E11" t="n">
         <v>24.4038</v>
       </c>
       <c r="F11" t="n">
-        <v>13.1297</v>
+        <v>13.1298</v>
       </c>
       <c r="G11" t="n">
         <v>30.6924</v>
@@ -1312,10 +1312,10 @@
         <v>17.5809</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.04179999999999939</v>
+        <v>-0.04179999999999984</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3394</v>
+        <v>2.3395</v>
       </c>
       <c r="U11" t="n">
         <v>-2.3813</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8881</v>
+        <v>-1.4291</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5803</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3078</v>
+        <v>-1.4947</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.6054</v>
+        <v>-3.8605</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4042</v>
+        <v>-1.6624</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2011</v>
+        <v>-2.1982</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2236</v>
+        <v>0.2099</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4644</v>
+        <v>-0.4247</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6879</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8289</v>
+        <v>-4.0705</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0601</v>
+        <v>-1.2377</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8891</v>
+        <v>-2.8328</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.1488</v>
+        <v>1.1721</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="S12" t="n">
-        <v>2.0465</v>
+        <v>0.6501</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8491</v>
+        <v>0.5552</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1974</v>
+        <v>0.0949</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8195</v>
+        <v>0.6093</v>
       </c>
       <c r="W12" t="n">
         <v>0.2772</v>
       </c>
       <c r="X12" t="n">
-        <v>0.5423</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.1502</v>
+        <v>-1.92</v>
       </c>
       <c r="E13" t="n">
-        <v>0.369</v>
+        <v>-1.6925</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5193</v>
+        <v>-0.2275</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.8605</v>
+        <v>-1.6054</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6624</v>
+        <v>-0.4042</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1982</v>
+        <v>-1.2011</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2099</v>
+        <v>0.2236</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4247</v>
+        <v>-0.4644</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.6879</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.0705</v>
+        <v>-1.8289</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2377</v>
+        <v>0.0601</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.8328</v>
+        <v>-1.8891</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1488</v>
+        <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9288999999999999</v>
+        <v>1.0146</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8586</v>
+        <v>0.7368</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0703</v>
+        <v>0.2778</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6093</v>
+        <v>0.8195</v>
       </c>
       <c r="W13" t="n">
         <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3321</v>
+        <v>0.5423</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.402</v>
+        <v>-2.0428</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4091</v>
+        <v>0.308</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.8111</v>
+        <v>-2.3508</v>
       </c>
       <c r="G14" t="n">
         <v>-4.0181</v>
@@ -1546,13 +1546,13 @@
         <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4973</v>
+        <v>-0.1382</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1845</v>
+        <v>0.0834</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6818</v>
+        <v>-0.2215</v>
       </c>
       <c r="V14" t="n">
         <v>0.9414</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.2569</v>
+        <v>-2.4207</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8647</v>
+        <v>1.6736</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.1216</v>
+        <v>-4.0944</v>
       </c>
       <c r="G15" t="n">
         <v>-4.8281</v>
@@ -1624,13 +1624,13 @@
         <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7962</v>
+        <v>0.04</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7455000000000001</v>
+        <v>0.0634</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0507</v>
+        <v>-0.0235</v>
       </c>
       <c r="V15" t="n">
         <v>0.6093</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.2733</v>
+        <v>-2.4436</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2247</v>
+        <v>-0.7192</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0485</v>
+        <v>-1.7244</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2929</v>
@@ -1702,13 +1702,13 @@
         <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7451</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5447</v>
+        <v>-0.0391</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2004</v>
+        <v>0.1238</v>
       </c>
       <c r="V16" t="n">
         <v>-1.0633</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. TURNQUEST</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.2904</v>
+        <v>-3.1319</v>
       </c>
       <c r="E17" t="n">
-        <v>0.61</v>
+        <v>-2.2971</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.9004</v>
+        <v>-0.8348</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1617</v>
+        <v>0.184</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1481</v>
+        <v>2.032</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0136</v>
+        <v>-1.848</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7227</v>
+        <v>0.7388</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0614</v>
+        <v>2.0466</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6613</v>
+        <v>-1.3077</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8844</v>
+        <v>-0.5548</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2095</v>
+        <v>-0.0146</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.5403</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>0.317</v>
+        <v>-0.4127</v>
       </c>
       <c r="T17" t="n">
-        <v>0.864</v>
+        <v>-0.1058</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.547</v>
+        <v>-0.3069</v>
       </c>
       <c r="V17" t="n">
-        <v>-3.4457</v>
+        <v>-1.3405</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.4457</v>
+        <v>-1.3405</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>E. TURNQUEST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.5511</v>
+        <v>-3.302</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9338</v>
+        <v>0.0033</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6173</v>
+        <v>-3.3053</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.699</v>
+        <v>-0.1617</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0665</v>
+        <v>-0.1481</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6324</v>
+        <v>-0.0136</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.4699</v>
+        <v>0.7227</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9171</v>
+        <v>0.0614</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5527</v>
+        <v>0.6613</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2291</v>
+        <v>-0.8844</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1494</v>
+        <v>-0.2095</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0797</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3163</v>
+        <v>0.3054</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2355</v>
+        <v>0.2573</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0808</v>
+        <v>0.0481</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.5591</v>
+        <v>-3.4457</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.8364</v>
+        <v>-3.4457</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.7917</v>
+        <v>-3.9491</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9038</v>
+        <v>-1.4394</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8879</v>
+        <v>-2.5097</v>
       </c>
       <c r="G19" t="n">
-        <v>0.184</v>
+        <v>-2.699</v>
       </c>
       <c r="H19" t="n">
-        <v>2.032</v>
+        <v>-1.0665</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.848</v>
+        <v>-1.6324</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7388</v>
+        <v>-1.4699</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0466</v>
+        <v>-0.9171</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3077</v>
+        <v>-0.5527</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5548</v>
+        <v>-1.2291</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0146</v>
+        <v>-0.1494</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5403</v>
+        <v>-1.0797</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
         <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0725</v>
+        <v>0.9183</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7125</v>
+        <v>0.7299</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.36</v>
+        <v>0.1883</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3405</v>
+        <v>-2.5591</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3405</v>
+        <v>-2.8364</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.8611</v>
+        <v>-6.0236</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.7696</v>
+        <v>-3.3652</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0915</v>
+        <v>-2.6584</v>
       </c>
       <c r="G20" t="n">
         <v>-4.48</v>
@@ -2014,13 +2014,13 @@
         <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3849</v>
+        <v>-0.5474</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5501</v>
+        <v>-0.1457</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8348</v>
+        <v>-0.4017</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9962</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-9.0688</v>
+        <v>-8.8485</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.9704</v>
+        <v>-5.667</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0984</v>
+        <v>-3.1815</v>
       </c>
       <c r="G21" t="n">
         <v>-8.930899999999999</v>
@@ -2092,13 +2092,13 @@
         <v>2.3441</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.1493</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0576</v>
+        <v>0.2457</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0134</v>
+        <v>-0.0964</v>
       </c>
       <c r="V21" t="n">
         <v>1.4959</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-37.53360000000001</v>
+        <v>-35.5113</v>
       </c>
       <c r="E22" t="n">
         <v>-13.1298</v>
       </c>
       <c r="F22" t="n">
-        <v>-24.4038</v>
+        <v>-22.3815</v>
       </c>
       <c r="G22" t="n">
         <v>-30.6926</v>
@@ -2143,7 +2143,7 @@
         <v>-21.5799</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.194599999999999</v>
+        <v>-3.1946</v>
       </c>
       <c r="K22" t="n">
         <v>-1.8522</v>
@@ -2170,13 +2170,13 @@
         <v>15.6275</v>
       </c>
       <c r="S22" t="n">
-        <v>0.04170000000000003</v>
+        <v>2.063999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3813</v>
+        <v>2.3811</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.3396</v>
+        <v>-0.3171</v>
       </c>
       <c r="V22" t="n">
         <v>-4.9294</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484303_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484303_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4714</v>
+        <v>0.914</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7805</v>
+        <v>0.914</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2519</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3888</v>
+        <v>0.914</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1689</v>
+        <v>0.307</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7801</v>
+        <v>0.607</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1444</v>
+        <v>0.914</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7887</v>
+        <v>0.307</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.6443</v>
+        <v>0.607</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2444</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3802</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1358</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4147</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6694</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2547</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. MAS CARDONA</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2993</v>
+        <v>0.5574</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4125</v>
+        <v>-1.6945</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7118</v>
+        <v>2.2519</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4413</v>
+        <v>1.4748</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1384</v>
+        <v>3.8619</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5797</v>
+        <v>-2.3871</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0417</v>
+        <v>1.2304</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0013</v>
+        <v>3.4817</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0405</v>
+        <v>-2.2513</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3996</v>
+        <v>0.2444</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1397</v>
+        <v>0.3802</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5393</v>
+        <v>-0.1358</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.5395</v>
       </c>
       <c r="S9" t="n">
-        <v>0.478</v>
+        <v>0.4147</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3708</v>
+        <v>0.6694</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1073</v>
+        <v>-0.2547</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>-0.9414</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. NDOYE</t>
+          <t>O. MAS CARDONA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.651</v>
+        <v>-0.2993</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4586</v>
+        <v>0.4125</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1924</v>
+        <v>-0.7118</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7235</v>
+        <v>0.4413</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.9637</v>
+        <v>-0.1384</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2402</v>
+        <v>0.5797</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.3175</v>
+        <v>0.0417</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.2886</v>
+        <v>0.0013</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9712</v>
+        <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>0.594</v>
+        <v>0.3996</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3249</v>
+        <v>-0.1397</v>
       </c>
       <c r="O10" t="n">
-        <v>0.269</v>
+        <v>0.5393</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0958</v>
+        <v>0.478</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3831</v>
+        <v>0.3708</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7127</v>
+        <v>0.1073</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2224</v>
+        <v>-1.2186</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.441</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>S. NDOYE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,301 +1317,317 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>37.53360000000001</v>
+        <v>-2.651</v>
       </c>
       <c r="E11" t="n">
-        <v>24.4038</v>
+        <v>-2.4586</v>
       </c>
       <c r="F11" t="n">
-        <v>13.1298</v>
+        <v>-0.1924</v>
       </c>
       <c r="G11" t="n">
-        <v>30.6924</v>
+        <v>-1.7235</v>
       </c>
       <c r="H11" t="n">
-        <v>9.112500000000001</v>
+        <v>-2.9637</v>
       </c>
       <c r="I11" t="n">
-        <v>21.58</v>
+        <v>1.2402</v>
       </c>
       <c r="J11" t="n">
-        <v>27.4978</v>
+        <v>-2.3175</v>
       </c>
       <c r="K11" t="n">
-        <v>7.260199999999999</v>
+        <v>-3.2886</v>
       </c>
       <c r="L11" t="n">
-        <v>20.2378</v>
+        <v>0.9712</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1948</v>
+        <v>0.594</v>
       </c>
       <c r="N11" t="n">
-        <v>1.8523</v>
+        <v>0.3249</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3422</v>
+        <v>0.269</v>
       </c>
       <c r="P11" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="Q11" t="n">
-        <v>-15.6273</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>17.5809</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.04179999999999984</v>
+        <v>-1.0958</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3395</v>
+        <v>-0.3831</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.3813</v>
+        <v>-0.7127</v>
       </c>
       <c r="V11" t="n">
-        <v>4.929399999999999</v>
+        <v>-0.2224</v>
       </c>
       <c r="W11" t="n">
-        <v>10.1937</v>
+        <v>1.2186</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.2643</v>
+        <v>-1.441</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4291</v>
+        <v>37.53360000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06569999999999999</v>
+        <v>24.4038</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4947</v>
+        <v>13.1298</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.8605</v>
+        <v>30.6924</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6624</v>
+        <v>9.112500000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1982</v>
+        <v>21.58</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2099</v>
+        <v>27.4978</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4247</v>
+        <v>7.260199999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6346000000000001</v>
+        <v>20.2378</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.0705</v>
+        <v>3.1948</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2377</v>
+        <v>1.8523</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.8328</v>
+        <v>1.3422</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-15.6273</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1488</v>
+        <v>17.5809</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6501</v>
+        <v>-0.04179999999999984</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5552</v>
+        <v>2.3395</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0949</v>
+        <v>-2.3813</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6093</v>
+        <v>4.929399999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>10.1937</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3321</v>
-      </c>
+        <v>-5.2643</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>J. BERTOMEU BALDÉ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.92</v>
+        <v>0.607</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6925</v>
+        <v>0.607</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2275</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.6054</v>
+        <v>0.607</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4042</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.2011</v>
+        <v>0.607</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2236</v>
+        <v>0.607</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4644</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6879</v>
+        <v>0.607</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.8289</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0601</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.8891</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0146</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7368</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2778</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8195</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5423</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.0428</v>
+        <v>0.307</v>
       </c>
       <c r="E14" t="n">
-        <v>0.308</v>
+        <v>0.307</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.3508</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.0181</v>
+        <v>0.307</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1051</v>
+        <v>0.307</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.9129</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0173</v>
+        <v>0.307</v>
       </c>
       <c r="K14" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.307</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0799</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.0008</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1678</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.833</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1382</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0834</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2215</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1572,621 +1638,989 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.4207</v>
+        <v>0.307</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6736</v>
+        <v>0.307</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.0944</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.8281</v>
+        <v>0.307</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.6854</v>
+        <v>0.307</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.1427</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3916</v>
+        <v>0.307</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.243</v>
+        <v>0.307</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6346000000000001</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.2196</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4423</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.7773</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0634</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0235</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.4436</v>
+        <v>-1.736</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7192</v>
+        <v>-0.2413</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7244</v>
+        <v>-1.4947</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2929</v>
+        <v>-4.1675</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9077</v>
+        <v>-1.9693</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2005</v>
+        <v>-2.1982</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9962</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9824000000000001</v>
+        <v>-0.7317</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0138</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2891</v>
+        <v>-4.0705</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0747</v>
+        <v>-1.2377</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2144</v>
+        <v>-2.8328</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1721</v>
+        <v>1.1721</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="S16" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.6501</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0391</v>
+        <v>0.5552</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1238</v>
+        <v>0.0949</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0633</v>
+        <v>0.6093</v>
       </c>
       <c r="W16" t="n">
         <v>0.2772</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3405</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.1319</v>
+        <v>-1.92</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2971</v>
+        <v>-1.6925</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8348</v>
+        <v>-0.2275</v>
       </c>
       <c r="G17" t="n">
-        <v>0.184</v>
+        <v>-1.6054</v>
       </c>
       <c r="H17" t="n">
-        <v>2.032</v>
+        <v>-0.4042</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.848</v>
+        <v>-1.2011</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7388</v>
+        <v>0.2236</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0466</v>
+        <v>-0.4644</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3077</v>
+        <v>0.6879</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5548</v>
+        <v>-1.8289</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0146</v>
+        <v>0.0601</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5403</v>
+        <v>-1.8891</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5627</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4127</v>
+        <v>1.0146</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1058</v>
+        <v>0.7368</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3069</v>
+        <v>0.2778</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.3405</v>
+        <v>0.8195</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3405</v>
+        <v>0.5423</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. TURNQUEST</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.302</v>
+        <v>-2.0428</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0033</v>
+        <v>0.308</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.3053</v>
+        <v>-2.3508</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1617</v>
+        <v>-4.0181</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1481</v>
+        <v>-1.1051</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0136</v>
+        <v>-2.9129</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7227</v>
+        <v>-0.0173</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0614</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6613</v>
+        <v>-0.0799</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8844</v>
+        <v>-4.0008</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2095</v>
+        <v>-1.1678</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-2.833</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3054</v>
+        <v>-0.1382</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2573</v>
+        <v>0.0834</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0481</v>
+        <v>-0.2215</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.4457</v>
+        <v>0.9414</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.4457</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.9491</v>
+        <v>-2.7277</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4394</v>
+        <v>1.3667</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5097</v>
+        <v>-4.0944</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.699</v>
+        <v>-5.1351</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0665</v>
+        <v>-1.9923</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6324</v>
+        <v>-3.1427</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4699</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9171</v>
+        <v>-0.55</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5527</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2291</v>
+        <v>-5.2196</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1494</v>
+        <v>-1.4423</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0797</v>
+        <v>-3.7773</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9183</v>
+        <v>0.04</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7299</v>
+        <v>0.0634</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1883</v>
+        <v>-0.0235</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.5591</v>
+        <v>0.6093</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.8364</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>J. BERTOMEU BALDE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.0236</v>
+        <v>-3.0506</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.3652</v>
+        <v>-1.3261</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6584</v>
+        <v>-1.7244</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.48</v>
+        <v>-0.8999</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0115</v>
+        <v>0.9077</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.4684</v>
+        <v>-1.8075</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2698</v>
+        <v>0.3892</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3646</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.09470000000000001</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.2101</v>
+        <v>-1.2891</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.647</v>
+        <v>-0.0747</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.5632</v>
+        <v>-1.2144</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5474</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1457</v>
+        <v>-0.0391</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4017</v>
+        <v>0.1238</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9962</v>
+        <v>-1.0633</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.9962</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.3405</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.8485</v>
+        <v>-3.1319</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.667</v>
+        <v>-2.2971</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1815</v>
+        <v>-0.8348</v>
       </c>
       <c r="G21" t="n">
-        <v>-8.930899999999999</v>
+        <v>0.184</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.9689</v>
+        <v>2.032</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.9621</v>
+        <v>-1.848</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.7204</v>
+        <v>0.7388</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.5915</v>
+        <v>2.0466</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.1289</v>
+        <v>-1.3077</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.2105</v>
+        <v>-0.5548</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3773</v>
+        <v>-0.0146</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.8332</v>
+        <v>-0.5403</v>
       </c>
       <c r="P21" t="n">
         <v>-1.5627</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.9069</v>
+        <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3441</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1493</v>
+        <v>-0.4127</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2457</v>
+        <v>-0.1058</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0964</v>
+        <v>-0.3069</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4959</v>
+        <v>-1.3405</v>
       </c>
       <c r="W21" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>-1.3405</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>E. TURNQUEST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-35.5113</v>
+        <v>-3.302</v>
       </c>
       <c r="E22" t="n">
-        <v>-13.1298</v>
+        <v>0.0033</v>
       </c>
       <c r="F22" t="n">
+        <v>-3.3053</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.1617</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.1481</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.0136</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.7227</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0614</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.6613</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.8844</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.2095</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.6749000000000001</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.2573</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.0481</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-3.4457</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-3.4457</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>R. DALET CASALPRIM</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-3.9491</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1.4394</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-2.5097</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2.699</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.0665</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.6324</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.4699</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.9171</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.5527</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.2291</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.1494</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.0797</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.9183</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.7299</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.1883</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-2.5591</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-2.8364</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>M. FONTANALS MARTIN</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-6.0236</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-3.3652</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-2.6584</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2.0115</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-2.4684</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.2698</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.3646</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-4.2101</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.647</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-2.5632</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.5474</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.1457</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.4017</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.9962</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.9962</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>R. FERNANDEZ DIAZ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-8.8485</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-5.667</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-3.1815</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-8.930899999999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-3.9689</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-4.9621</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-4.7204</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-2.5915</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-2.1289</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-4.2105</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.3773</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-2.8332</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.3441</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.1493</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.2457</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.0964</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.7145</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484303_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-35.5112</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-13.1296</v>
+      </c>
+      <c r="F26" t="n">
         <v>-22.3815</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G26" t="n">
         <v>-30.6926</v>
       </c>
-      <c r="H22" t="n">
-        <v>-9.112399999999999</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="H26" t="n">
+        <v>-9.1122</v>
+      </c>
+      <c r="I26" t="n">
         <v>-21.5799</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J26" t="n">
         <v>-3.1946</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K26" t="n">
         <v>-1.8522</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L26" t="n">
         <v>-1.3423</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M26" t="n">
         <v>-27.4978</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N26" t="n">
         <v>-7.2602</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O26" t="n">
         <v>-20.2379</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P26" t="n">
         <v>-1.9533</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q26" t="n">
         <v>-17.5807</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R26" t="n">
         <v>15.6275</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.063999999999999</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="S26" t="n">
+        <v>2.064</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.3811</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U26" t="n">
         <v>-0.3171</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V26" t="n">
         <v>-4.9294</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W26" t="n">
         <v>5.2643</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X26" t="n">
         <v>-10.1938</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
